--- a/03 학년말성적/20929 김온주.xlsx
+++ b/03 학년말성적/20929 김온주.xlsx
@@ -175,7 +175,7 @@
     <t>제품별 상품사슬 탐구하기</t>
   </si>
   <si>
-    <t>무원고등학교</t>
+    <t>oo고등학교</t>
   </si>
   <si>
     <t>1 / 2</t>
